--- a/Config/Excel/Tables/常量表.xlsx
+++ b/Config/Excel/Tables/常量表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25440" windowHeight="9435"/>
+    <workbookView windowWidth="28800" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>##column#var</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>登录中心服Id</t>
+  </si>
+  <si>
+    <t>DefaultRoleId</t>
+  </si>
+  <si>
+    <t>默认角色</t>
   </si>
 </sst>
 </file>
@@ -1011,8 +1017,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="29.625" customWidth="1"/>
     <col min="3" max="3" width="19.2833333333333" customWidth="1"/>
@@ -1078,6 +1084,20 @@
       </c>
       <c r="D6">
         <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
